--- a/05_dior_photos/dior_photo_metadata.xlsx
+++ b/05_dior_photos/dior_photo_metadata.xlsx
@@ -310,7 +310,7 @@
     </x:row>
     <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>IMG_006321.png</x:v>
+        <x:v>IMG_006321.jpg</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
         <x:v>DIOR_CHAIR</x:v>
@@ -330,7 +330,7 @@
     </x:row>
     <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>IMG_006326.png</x:v>
+        <x:v>IMG_006326.jpg</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
         <x:v>DIOR_CHAIR</x:v>
@@ -350,7 +350,7 @@
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="9" t="str">
-        <x:v>IMG_006332.png</x:v>
+        <x:v>IMG_006332.jpg</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
         <x:v>DIOR_CHAIR</x:v>
@@ -370,7 +370,7 @@
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="9" t="str">
-        <x:v>IMG_003714.png</x:v>
+        <x:v>IMG_003714.jpg</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
         <x:v>DIOR_ANIMALS</x:v>
@@ -390,7 +390,7 @@
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="9" t="str">
-        <x:v>IMG_003719.png</x:v>
+        <x:v>IMG_003719.jpg</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
         <x:v>DIOR_ANIMALS</x:v>
@@ -457,7 +457,7 @@
     </x:row>
     <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>IMG_006321.png</x:v>
+        <x:v>IMG_006321.jpg</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
         <x:v>direct</x:v>
@@ -469,7 +469,7 @@
     </x:row>
     <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>IMG_006326.png</x:v>
+        <x:v>IMG_006326.jpg</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
         <x:v>direct</x:v>
@@ -481,13 +481,13 @@
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="9" t="str">
-        <x:v>IMG_006332.png</x:v>
+        <x:v>IMG_006332.jpg</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
         <x:v>contextual</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>IMG_006321.png, IMG_006326.png</x:v>
+        <x:v>IMG_006321.jpg, IMG_006326.jpg</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
         <x:v>같은 방문 ID·장소, 인접 촬영시간, 동일 인물과 의상으로 연결</x:v>
@@ -495,7 +495,7 @@
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="9" t="str">
-        <x:v>IMG_003714.png</x:v>
+        <x:v>IMG_003714.jpg</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
         <x:v>direct</x:v>
@@ -507,7 +507,7 @@
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="9" t="str">
-        <x:v>IMG_003719.png</x:v>
+        <x:v>IMG_003719.jpg</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
         <x:v>direct</x:v>
